--- a/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81992</t>
+          <t>82589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100001</t>
+          <t>99939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>45493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>85176</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108342</t>
+          <t>108408</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149490</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>176681</t>
+          <t>176327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>62303</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>88869</t>
+          <t>90301</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>56696</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>72465</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>126225</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>158483</t>
+          <t>159916</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>77592</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>73918</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>128756</t>
+          <t>128844</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>148274</t>
+          <t>147959</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>396</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,82 +6750,82 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>6565</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
-          <t>11313</t>
-        </is>
-      </c>
-      <c r="U57" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>21170</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>49281</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>33649</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>68161</t>
+          <t>66697</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>100708</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>511856</t>
+          <t>510709</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>561089</t>
+          <t>560991</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,82 +720,82 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9185</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9380</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1511,47 +1511,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4714</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1624,72 +1624,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13757</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4024</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>923</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7914</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8798</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13297</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47786</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39924</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54703</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41903</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36589</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45964</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56310</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91835</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82589</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99939</t>
+          <t>98564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,47 +2080,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2193,82 +2193,82 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5227</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2306,82 +2306,82 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5096</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>945</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2419,82 +2419,82 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>323</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2532,82 +2532,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5279</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2645,72 +2645,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>4187</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>864</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>864</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -2871,47 +2871,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>358</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6511</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>11183</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>6059</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3054</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10845</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>18562</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>12370</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>32996</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>26,18%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>10237</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>6238</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>16736</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>30243</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>92627</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>78477</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>100667</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>73,49%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>64816</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>56771</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>70841</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>73,83%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>64,67%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>80,7%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>99526</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85176</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108408</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>164342</t>
+          <t>156785</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149869</t>
+          <t>143340</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>176327</t>
+          <t>168483</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>86748</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>86748</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>86748</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>135607</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>135607</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>135607</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>326</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3553,72 +3553,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5899</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4005,47 +4005,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>4897</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>1591</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>5830</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>806</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4123,32 +4123,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,32 +4158,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -4231,72 +4231,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>7280</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1692</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>4789</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>367</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>10283</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>5370</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1699</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>10489</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>6077</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>11340</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>7747</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>14969</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>14,98%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>56993</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>49515</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>63712</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>75450</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>62303</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>90301</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>75,51%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>62,35%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>56769</t>
+          <t>38738</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>72465</t>
+          <t>52993</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>126225</t>
+          <t>93776</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>159916</t>
+          <t>114014</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>71566</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>71566</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>71566</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,82 +4800,82 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>5799</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>4463</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4913,107 +4913,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>9614</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5026,82 +5026,82 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5139,72 +5139,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>3812</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>866</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>6041</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5769,42 +5769,42 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>6937</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>15749</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>11472</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>7159</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>17634</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>63332</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>56388</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>69849</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>67,51%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>83,62%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>71506</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>65194</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>77592</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>80,36%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>62247</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>74075</t>
+          <t>74420</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>138922</t>
+          <t>132085</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>128844</t>
+          <t>121724</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>147959</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>89650</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>89650</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>89650</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>243</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6160,72 +6160,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6273,72 +6273,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>14168</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5956</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>8058</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>13975</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6386,82 +6386,82 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6499,47 +6499,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6574,17 +6574,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>326</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6612,72 +6612,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>12222</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6725,72 +6725,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>7286</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6951,107 +6951,107 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>4046</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>9413</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>11723</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2970</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>10158</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>9895</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>17011</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>4487</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>10128</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>10547</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>17179</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7064,72 +7064,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>19070</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>12017</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>26732</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>13890</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>8499</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>21682</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>42688</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>48455</t>
+          <t>58895</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>50121</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>66697</t>
+          <t>69848</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>100708</t>
+          <t>99588</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>253675</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>239906</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>273005</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208646</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>510709</t>
+          <t>461960</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>560991</t>
+          <t>501963</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>979</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
